--- a/practice-files/day06-透视表基础.xlsx
+++ b/practice-files/day06-透视表基础.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销售明细" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,19 +568,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -634,12 +620,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -649,121 +635,121 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>2820.24</v>
+        <v>1112.02</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>5640.48</v>
+        <v>1112.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2524.7</v>
+        <v>2345.95</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>10098.8</v>
+        <v>9383.799999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>761.99</v>
+        <v>102.62</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1523.98</v>
+        <v>307.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2925.01</v>
+        <v>2367.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>5850.02</v>
+        <v>2367.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -773,157 +759,157 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>487.92</v>
+        <v>621.73</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1463.76</v>
+        <v>2486.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>770.87</v>
+        <v>1989.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3083.48</v>
+        <v>7957.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>886.73</v>
+        <v>1934.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1773.46</v>
+        <v>7736.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1552.46</v>
+        <v>1753.35</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3104.92</v>
+        <v>5260.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>388.31</v>
+        <v>1325.09</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>776.62</v>
+        <v>1325.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -932,60 +918,60 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1206.49</v>
+        <v>2134.09</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2412.98</v>
+        <v>2134.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1580.07</v>
+        <v>1879.77</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3160.14</v>
+        <v>1879.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -994,86 +980,86 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2175.7</v>
+        <v>1224.13</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4351.4</v>
+        <v>3672.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>281.87</v>
+        <v>1857.08</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>845.61</v>
+        <v>5571.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1893.66</v>
+        <v>653.24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1893.66</v>
+        <v>1959.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1083,59 +1069,59 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2912.94</v>
+        <v>1434.36</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>8738.82</v>
+        <v>2868.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1060.14</v>
+        <v>2027.2</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2120.28</v>
+        <v>4054.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1145,33 +1131,33 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2145.36</v>
+        <v>2951.29</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6436.08</v>
+        <v>2951.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1180,86 +1166,86 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>241.31</v>
+        <v>1215.97</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>965.24</v>
+        <v>2431.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1709.59</v>
+        <v>551.38</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1709.59</v>
+        <v>2205.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>112.53</v>
+        <v>425.02</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>112.53</v>
+        <v>1700.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1269,152 +1255,152 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2968.69</v>
+        <v>1296.42</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2968.69</v>
+        <v>5185.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2941.04</v>
+        <v>2261.78</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>11764.16</v>
+        <v>6785.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2461.09</v>
+        <v>259.13</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>9844.360000000001</v>
+        <v>777.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>928.4400000000001</v>
+        <v>268.32</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1856.88</v>
+        <v>536.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1259.81</v>
+        <v>1261.16</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1259.81</v>
+        <v>3783.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>卫衣连帽</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1424,54 +1410,54 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2507.89</v>
+        <v>1185.75</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7523.67</v>
+        <v>1185.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>804.79</v>
+        <v>2266.82</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2414.37</v>
+        <v>9067.280000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1486,121 +1472,121 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>471.28</v>
+        <v>1471.36</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>942.5599999999999</v>
+        <v>5885.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2591.12</v>
+        <v>2760.04</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2591.12</v>
+        <v>2760.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1317.74</v>
+        <v>432.03</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3953.22</v>
+        <v>1728.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2726.04</v>
+        <v>657.63</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2726.04</v>
+        <v>1972.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1610,209 +1596,209 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>230.39</v>
+        <v>778.25</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>460.78</v>
+        <v>778.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>737.8099999999999</v>
+        <v>1959.93</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2951.24</v>
+        <v>1959.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2600.19</v>
+        <v>481.58</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5200.38</v>
+        <v>963.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2393.39</v>
+        <v>1410.15</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>7180.17</v>
+        <v>4230.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>229.27</v>
+        <v>350.05</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>917.08</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>843.54</v>
+        <v>254.71</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2530.62</v>
+        <v>509.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2355.45</v>
+        <v>2393.79</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2355.45</v>
+        <v>2393.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -1827,550 +1813,550 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>842.64</v>
+        <v>1531.7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>842.64</v>
+        <v>4595.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2576.4</v>
+        <v>1316.56</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2576.4</v>
+        <v>3949.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2024.38</v>
+        <v>2208.37</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2024.38</v>
+        <v>6625.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>571.5599999999999</v>
+        <v>986.24</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>571.5599999999999</v>
+        <v>1972.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2185.94</v>
+        <v>1721.45</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>4371.88</v>
+        <v>6885.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>492.62</v>
+        <v>1477.02</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>985.24</v>
+        <v>4431.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>362.82</v>
+        <v>1679.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1088.46</v>
+        <v>3359.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1116.52</v>
+        <v>2280.75</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>2233.04</v>
+        <v>9123</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>461.21</v>
+        <v>687.14</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>461.21</v>
+        <v>1374.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>869.04</v>
+        <v>1605.84</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>869.04</v>
+        <v>6423.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>瑜伽垫</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2598.99</v>
+        <v>775.67</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>7796.97</v>
+        <v>775.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2992.38</v>
+        <v>597.88</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>8977.139999999999</v>
+        <v>2391.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2194.04</v>
+        <v>908.85</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>2194.04</v>
+        <v>2726.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1449.11</v>
+        <v>843.7</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>2898.22</v>
+        <v>843.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1316</v>
+        <v>2620.98</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>5264</v>
+        <v>7862.94</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>iPad Air</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2104.89</v>
+        <v>2896.53</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>4209.78</v>
+        <v>8689.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>610.45</v>
+        <v>249.02</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1220.9</v>
+        <v>249.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2585.97</v>
+        <v>380.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2585.97</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -2385,48 +2371,48 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1877.97</v>
+        <v>912.14</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>7511.88</v>
+        <v>3648.56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>380.62</v>
+        <v>2843.34</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>380.62</v>
+        <v>5686.68</v>
       </c>
     </row>
     <row r="60">
@@ -2437,38 +2423,38 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>显示器</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1650.26</v>
+        <v>545.23</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>3300.52</v>
+        <v>545.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>毛巾</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2478,59 +2464,59 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1598.75</v>
+        <v>1424.64</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1598.75</v>
+        <v>1424.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2041.07</v>
+        <v>2070.53</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>8164.28</v>
+        <v>6211.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2540,276 +2526,276 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2466.55</v>
+        <v>1952.48</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>9866.200000000001</v>
+        <v>5857.44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1660.06</v>
+        <v>1796.28</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>6640.24</v>
+        <v>5388.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2994</v>
+        <v>2828.75</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>5988</v>
+        <v>11315</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>175.31</v>
+        <v>1822.03</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>175.31</v>
+        <v>1822.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>燕窝</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2831.71</v>
+        <v>148.49</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>11326.84</v>
+        <v>296.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>143.97</v>
+        <v>2989.93</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>431.91</v>
+        <v>11959.72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2938.88</v>
+        <v>1018.93</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>8816.639999999999</v>
+        <v>1018.93</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1043.86</v>
+        <v>1996.87</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>4175.44</v>
+        <v>7987.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>794.84</v>
+        <v>989.12</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>2384.52</v>
+        <v>3956.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2819,90 +2805,90 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>747.02</v>
+        <v>586.12</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1494.04</v>
+        <v>1758.36</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>263.14</v>
+        <v>822.16</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>789.42</v>
+        <v>1644.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1481.44</v>
+        <v>2919.25</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1481.44</v>
+        <v>5838.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -2916,117 +2902,117 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>588.9</v>
+        <v>305.83</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1766.7</v>
+        <v>305.83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1822.09</v>
+        <v>1540.35</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>3644.18</v>
+        <v>4621.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>567.61</v>
+        <v>1385.66</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>567.61</v>
+        <v>2771.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2216.08</v>
+        <v>2323.85</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>2216.08</v>
+        <v>9295.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3036,64 +3022,64 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2887.34</v>
+        <v>2185.37</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>5774.68</v>
+        <v>8741.48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1182.63</v>
+        <v>1668.19</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>4730.52</v>
+        <v>6672.76</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>运动短裤</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3105,305 +3091,305 @@
         <v>4</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2492.94</v>
+        <v>1166.42</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>9971.76</v>
+        <v>4665.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2606.83</v>
+        <v>2964.59</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5213.66</v>
+        <v>5929.18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>AirPods Pro</t>
+          <t>望远镜</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1181.61</v>
+        <v>1015.02</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3544.83</v>
+        <v>1015.02</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>iPad Air</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>1246.64</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>272.72</v>
+        <v>2493.28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>燕窝</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2445.91</v>
+        <v>2086.33</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>2445.91</v>
+        <v>2086.33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2774.88</v>
+        <v>2619.98</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2774.88</v>
+        <v>2619.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>542.8099999999999</v>
+        <v>1317.9</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>542.8099999999999</v>
+        <v>1317.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2165.05</v>
+        <v>165.59</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>2165.05</v>
+        <v>165.59</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2475.75</v>
+        <v>754.27</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>9903</v>
+        <v>3017.08</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>425.73</v>
+        <v>2615.39</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1277.19</v>
+        <v>5230.78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3412,24 +3398,24 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2463.6</v>
+        <v>1923.58</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>4927.2</v>
+        <v>7694.32</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3439,141 +3425,141 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2428.52</v>
+        <v>2041.5</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>2428.52</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>570.37</v>
+        <v>1926.65</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1140.74</v>
+        <v>7706.6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1001.42</v>
+        <v>2563.41</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2002.84</v>
+        <v>2563.41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2278.02</v>
+        <v>2977.3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>2278.02</v>
+        <v>8931.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2236.76</v>
+        <v>1709.81</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>8947.040000000001</v>
+        <v>1709.81</v>
       </c>
     </row>
     <row r="97">
@@ -3584,69 +3570,69 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>运动短裤</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1034.44</v>
+        <v>2410.74</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4137.76</v>
+        <v>4821.48</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1348.31</v>
+        <v>2712.11</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>5393.24</v>
+        <v>2712.11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3656,90 +3642,90 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>394.94</v>
+        <v>1112.64</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>789.88</v>
+        <v>2225.28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1588.2</v>
+        <v>625.36</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>4764.6</v>
+        <v>1876.08</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2416.48</v>
+        <v>2902.13</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>2416.48</v>
+        <v>8706.389999999999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -3753,19 +3739,19 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1996.29</v>
+        <v>447.05</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1996.29</v>
+        <v>894.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -3780,59 +3766,59 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1987.59</v>
+        <v>70.34</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>3975.18</v>
+        <v>70.34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>卫衣连帽</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1238.55</v>
+        <v>2471.58</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>3715.65</v>
+        <v>7414.74</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -3849,52 +3835,52 @@
         <v>3</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>516.75</v>
+        <v>1869.05</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>1550.25</v>
+        <v>5607.15</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1713.05</v>
+        <v>1957.24</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1713.05</v>
+        <v>1957.24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -3904,28 +3890,28 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>2405.03</v>
+        <v>373.88</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>9620.120000000001</v>
+        <v>747.76</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -3935,64 +3921,64 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1325.01</v>
+        <v>1273.81</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>3975.03</v>
+        <v>2547.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>毛巾</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>987.24</v>
+        <v>1241.1</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3948.96</v>
+        <v>3723.3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -4001,44 +3987,44 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>2500.77</v>
+        <v>1349.75</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>10003.08</v>
+        <v>2699.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>卫衣连帽</t>
+          <t>羽毛球拍</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>150.41</v>
+        <v>208.83</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>300.82</v>
+        <v>626.49</v>
       </c>
     </row>
   </sheetData>

--- a/practice-files/day06-透视表基础.xlsx
+++ b/practice-files/day06-透视表基础.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -552,6 +552,13 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   WPS提示：WPS的切片器入口不同——先点击选中透视表→顶部出现"数据透视表工具"→在"分析"选项卡里点"插入切片器"（WPS 2019以上版本才有）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>4. 试试：同一个透视表同时看"各城市×各分类"的交叉销售额（行=城市，列=分类，值=金额求和）</t>
         </is>
@@ -620,12 +627,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -635,59 +642,59 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1112.02</v>
+        <v>2231.4</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1112.02</v>
+        <v>4462.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2345.95</v>
+        <v>1782.76</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>9383.799999999999</v>
+        <v>1782.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -697,183 +704,183 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>102.62</v>
+        <v>1817</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>307.86</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2367.5</v>
+        <v>2433.01</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2367.5</v>
+        <v>2433.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>621.73</v>
+        <v>490.77</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2486.92</v>
+        <v>1472.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1989.3</v>
+        <v>2546.06</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7957.2</v>
+        <v>7638.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1934.2</v>
+        <v>2919.15</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7736.8</v>
+        <v>11676.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>羽毛球拍</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1753.35</v>
+        <v>1743.74</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5260.05</v>
+        <v>1743.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -883,28 +890,28 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1325.09</v>
+        <v>2569.29</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1325.09</v>
+        <v>2569.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -914,374 +921,374 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2134.09</v>
+        <v>1128.44</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2134.09</v>
+        <v>2256.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1879.77</v>
+        <v>1615.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1879.77</v>
+        <v>3230.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1224.13</v>
+        <v>681.26</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3672.39</v>
+        <v>2043.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1857.08</v>
+        <v>824.1900000000001</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5571.24</v>
+        <v>1648.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>653.24</v>
+        <v>453.33</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1959.72</v>
+        <v>906.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>围巾</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1434.36</v>
+        <v>2695.53</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2868.72</v>
+        <v>10782.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2027.2</v>
+        <v>299</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4054.4</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>毛巾</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2951.29</v>
+        <v>217.68</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2951.29</v>
+        <v>870.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1215.97</v>
+        <v>2049.44</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2431.94</v>
+        <v>2049.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>551.38</v>
+        <v>1320.25</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2205.52</v>
+        <v>5281</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>425.02</v>
+        <v>1536.81</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1700.08</v>
+        <v>1536.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1296.42</v>
+        <v>2293.66</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5185.68</v>
+        <v>2293.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1293,83 +1300,83 @@
         <v>3</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2261.78</v>
+        <v>2638.8</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6785.34</v>
+        <v>7916.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>259.13</v>
+        <v>283.39</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>777.39</v>
+        <v>1133.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>268.32</v>
+        <v>2841.14</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>536.64</v>
+        <v>5682.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1379,183 +1386,183 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1261.16</v>
+        <v>2272.14</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3783.48</v>
+        <v>4544.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1185.75</v>
+        <v>1369.91</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1185.75</v>
+        <v>2739.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2266.82</v>
+        <v>1674.15</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9067.280000000001</v>
+        <v>3348.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1471.36</v>
+        <v>2718.1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5885.44</v>
+        <v>8154.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2760.04</v>
+        <v>665.28</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2760.04</v>
+        <v>1330.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>432.03</v>
+        <v>309.15</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1728.12</v>
+        <v>1236.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1565,59 +1572,59 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>657.63</v>
+        <v>2028.89</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1972.89</v>
+        <v>2028.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>778.25</v>
+        <v>598.02</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>778.25</v>
+        <v>2392.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1627,28 +1634,28 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1959.93</v>
+        <v>770.9299999999999</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1959.93</v>
+        <v>770.9299999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1658,219 +1665,219 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>481.58</v>
+        <v>2512</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>963.16</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1410.15</v>
+        <v>663.83</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4230.45</v>
+        <v>2655.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>350.05</v>
+        <v>816.65</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>350.05</v>
+        <v>3266.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>254.71</v>
+        <v>910.22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>509.42</v>
+        <v>910.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2393.79</v>
+        <v>1764.01</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2393.79</v>
+        <v>3528.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1531.7</v>
+        <v>1796.25</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4595.1</v>
+        <v>3592.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>望远镜</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1316.56</v>
+        <v>147.03</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>3949.68</v>
+        <v>147.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1882,109 +1889,109 @@
         <v>3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2208.37</v>
+        <v>2018.09</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>6625.11</v>
+        <v>6054.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>986.24</v>
+        <v>1386.96</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1972.48</v>
+        <v>1386.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1721.45</v>
+        <v>662.0700000000001</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>6885.8</v>
+        <v>1986.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1477.02</v>
+        <v>875.41</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4431.06</v>
+        <v>3501.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -1999,95 +2006,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1679.7</v>
+        <v>2796.32</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>3359.4</v>
+        <v>2796.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>显示器</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2280.75</v>
+        <v>490.68</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>9123</v>
+        <v>1472.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>687.14</v>
+        <v>1530.06</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1374.28</v>
+        <v>4590.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2096,55 +2103,55 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1605.84</v>
+        <v>39.53</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>6423.36</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>775.67</v>
+        <v>1694.89</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>775.67</v>
+        <v>1694.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2154,64 +2161,64 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>597.88</v>
+        <v>2507.75</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>2391.52</v>
+        <v>5015.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>908.85</v>
+        <v>2698.98</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>2726.55</v>
+        <v>2698.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2220,50 +2227,50 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>843.7</v>
+        <v>2345.95</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>843.7</v>
+        <v>9383.799999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2620.98</v>
+        <v>102.62</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>7862.94</v>
+        <v>307.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -2278,28 +2285,28 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2896.53</v>
+        <v>2367.5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>8689.59</v>
+        <v>2367.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2309,276 +2316,276 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>249.02</v>
+        <v>621.73</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>249.02</v>
+        <v>2486.92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>380.8</v>
+        <v>1989.3</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1523.2</v>
+        <v>7957.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>912.14</v>
+        <v>1934.2</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3648.56</v>
+        <v>7736.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2843.34</v>
+        <v>1753.35</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>5686.68</v>
+        <v>5260.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>蜂蜜柚子茶</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>545.23</v>
+        <v>1325.09</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>545.23</v>
+        <v>1325.09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1424.64</v>
+        <v>2134.09</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1424.64</v>
+        <v>2134.09</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2070.53</v>
+        <v>1879.77</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6211.59</v>
+        <v>1879.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1952.48</v>
+        <v>1224.13</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>5857.44</v>
+        <v>3672.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1796.28</v>
+        <v>1857.08</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>5388.84</v>
+        <v>5571.24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2588,152 +2595,152 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2828.75</v>
+        <v>653.24</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>11315</v>
+        <v>1959.72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1822.03</v>
+        <v>1434.36</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>1822.03</v>
+        <v>2868.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>148.49</v>
+        <v>2027.2</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>296.98</v>
+        <v>4054.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2989.93</v>
+        <v>2951.29</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>11959.72</v>
+        <v>2951.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1018.93</v>
+        <v>1215.97</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1018.93</v>
+        <v>2431.94</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2743,33 +2750,33 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1996.87</v>
+        <v>551.38</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>7987.48</v>
+        <v>2205.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2781,26 +2788,26 @@
         <v>4</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>989.12</v>
+        <v>425.02</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>3956.48</v>
+        <v>1700.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2809,91 +2816,91 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>586.12</v>
+        <v>1296.42</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1758.36</v>
+        <v>5185.68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>822.16</v>
+        <v>2261.78</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1644.32</v>
+        <v>6785.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2919.25</v>
+        <v>259.13</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>5838.5</v>
+        <v>777.39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2902,210 +2909,210 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>305.83</v>
+        <v>268.32</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>305.83</v>
+        <v>536.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1540.35</v>
+        <v>1261.16</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>4621.05</v>
+        <v>3783.48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1385.66</v>
+        <v>1185.75</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>2771.32</v>
+        <v>1185.75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2323.85</v>
+        <v>2266.82</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>9295.4</v>
+        <v>9067.280000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2185.37</v>
+        <v>1471.36</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>8741.48</v>
+        <v>5885.44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1668.19</v>
+        <v>2760.04</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>6672.76</v>
+        <v>2760.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1166.42</v>
+        <v>432.03</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>4665.68</v>
+        <v>1728.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3115,152 +3122,152 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2964.59</v>
+        <v>657.63</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>5929.18</v>
+        <v>1972.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1015.02</v>
+        <v>778.25</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>1015.02</v>
+        <v>778.25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>iPad Air</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1246.64</v>
+        <v>1959.93</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>2493.28</v>
+        <v>1959.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2086.33</v>
+        <v>481.58</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>2086.33</v>
+        <v>963.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2619.98</v>
+        <v>1410.15</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2619.98</v>
+        <v>4230.45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3270,152 +3277,152 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1317.9</v>
+        <v>350.05</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1317.9</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>165.59</v>
+        <v>254.71</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>165.59</v>
+        <v>509.42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>754.27</v>
+        <v>2393.79</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>3017.08</v>
+        <v>2393.79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2615.39</v>
+        <v>1531.7</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>5230.78</v>
+        <v>4595.1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1923.58</v>
+        <v>1316.56</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>7694.32</v>
+        <v>3949.68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3425,23 +3432,23 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2041.5</v>
+        <v>2208.37</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>4083</v>
+        <v>6625.11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -3456,28 +3463,28 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1926.65</v>
+        <v>986.24</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>7706.6</v>
+        <v>1972.48</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -3487,343 +3494,343 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2563.41</v>
+        <v>1721.45</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2563.41</v>
+        <v>6885.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2977.3</v>
+        <v>1477.02</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>8931.9</v>
+        <v>4431.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1709.81</v>
+        <v>1679.7</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1709.81</v>
+        <v>3359.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2410.74</v>
+        <v>2280.75</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4821.48</v>
+        <v>9123</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2712.11</v>
+        <v>687.14</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>2712.11</v>
+        <v>1374.28</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1112.64</v>
+        <v>1605.84</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>2225.28</v>
+        <v>6423.36</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>625.36</v>
+        <v>775.67</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>1876.08</v>
+        <v>775.67</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2902.13</v>
+        <v>597.88</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>8706.389999999999</v>
+        <v>2391.52</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>447.05</v>
+        <v>908.85</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>894.1</v>
+        <v>2726.55</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>70.34</v>
+        <v>843.7</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>70.34</v>
+        <v>843.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
         <v>3</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>2471.58</v>
+        <v>2620.98</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>7414.74</v>
+        <v>7862.94</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3835,21 +3842,21 @@
         <v>3</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1869.05</v>
+        <v>2896.53</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>5607.15</v>
+        <v>8689.59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -3859,121 +3866,121 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1957.24</v>
+        <v>249.02</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1957.24</v>
+        <v>249.02</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>373.88</v>
+        <v>380.8</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>747.76</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1273.81</v>
+        <v>912.14</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>2547.62</v>
+        <v>3648.56</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1241.1</v>
+        <v>2843.34</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3723.3</v>
+        <v>5686.68</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -3983,48 +3990,48 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1349.75</v>
+        <v>545.23</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>2699.5</v>
+        <v>545.23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>毛巾</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>208.83</v>
+        <v>1424.64</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>626.49</v>
+        <v>1424.64</v>
       </c>
     </row>
   </sheetData>

--- a/practice-files/day06-透视表基础.xlsx
+++ b/practice-files/day06-透视表基础.xlsx
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="20" hidden="1" outlineLevel="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 行/列=按什么分类；值=汇总计算什么（计数/求和/平均）；筛选器=整体按什么条件过滤。</t>
+          <t>答案: 行/列=按什么分类；值=汇总计算什么（计数/求和/平均）；筛选器=整体按什么条件过滤。</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
     <row r="23" hidden="1" outlineLevel="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 数字默认求和、文本默认计数。要平均值：点值字段→值字段设置→汇总方式选"平均值"。</t>
+          <t>答案: 数字默认求和、文本默认计数。要平均值：点值字段→值字段设置→汇总方式选"平均值"。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day06-透视表基础.xlsx
+++ b/practice-files/day06-透视表基础.xlsx
@@ -683,260 +683,260 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>1112.02</v>
+        <v>2817.68</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>1112.02</v>
+        <v>5635.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>2345.95</v>
+        <v>163.55</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9383.799999999999</v>
+        <v>327.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>102.62</v>
+        <v>471.35</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>307.86</v>
+        <v>942.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2367.5</v>
+        <v>2971.13</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2367.5</v>
+        <v>8913.389999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>621.73</v>
+        <v>1439.43</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2486.92</v>
+        <v>1439.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>毛巾</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1989.3</v>
+        <v>942.8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>7957.2</v>
+        <v>942.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1934.2</v>
+        <v>1455.93</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>7736.8</v>
+        <v>5823.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1753.35</v>
+        <v>2845.17</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>5260.05</v>
+        <v>2845.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>红酒</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -946,33 +946,33 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1325.09</v>
+        <v>478.75</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1325.09</v>
+        <v>957.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>iPad Air</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -981,29 +981,29 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>2134.09</v>
+        <v>1569.49</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2134.09</v>
+        <v>4708.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1012,86 +1012,86 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1879.77</v>
+        <v>1394.2</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1879.77</v>
+        <v>4182.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1224.13</v>
+        <v>600.02</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3672.39</v>
+        <v>1200.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1857.08</v>
+        <v>2319.39</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>5571.24</v>
+        <v>4638.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>橄榄油</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1101,59 +1101,59 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>653.24</v>
+        <v>2802.09</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1959.72</v>
+        <v>8406.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>围巾</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1434.36</v>
+        <v>2864.19</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2868.72</v>
+        <v>5728.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1163,33 +1163,33 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2027.2</v>
+        <v>2773.31</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4054.4</v>
+        <v>8319.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -1198,29 +1198,29 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2951.29</v>
+        <v>2800.08</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2951.29</v>
+        <v>8400.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1232,21 +1232,21 @@
         <v>2</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>1215.97</v>
+        <v>2018.41</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>2431.94</v>
+        <v>4036.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1256,457 +1256,457 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>551.38</v>
+        <v>2159.55</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2205.52</v>
+        <v>2159.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>425.02</v>
+        <v>1447.02</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>1700.08</v>
+        <v>2894.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>AirPods Pro</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1296.42</v>
+        <v>1966.33</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>5185.68</v>
+        <v>3932.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>2261.78</v>
+        <v>2990.6</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>6785.34</v>
+        <v>11962.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>259.13</v>
+        <v>915.22</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>777.39</v>
+        <v>915.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>268.32</v>
+        <v>1495.92</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>536.64</v>
+        <v>2991.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1261.16</v>
+        <v>511.61</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>3783.48</v>
+        <v>2046.44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1185.75</v>
+        <v>2377.58</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>1185.75</v>
+        <v>4755.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>2266.82</v>
+        <v>1002.94</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>9067.280000000001</v>
+        <v>4011.76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1471.36</v>
+        <v>2808.4</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>5885.44</v>
+        <v>2808.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2760.04</v>
+        <v>2862.48</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2760.04</v>
+        <v>8587.440000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>432.03</v>
+        <v>2012.32</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>1728.12</v>
+        <v>8049.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>657.63</v>
+        <v>2079.16</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>1972.89</v>
+        <v>6237.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>778.25</v>
+        <v>1449.2</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>778.25</v>
+        <v>5796.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>1959.93</v>
+        <v>2291.72</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1959.93</v>
+        <v>2291.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -1721,28 +1721,28 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>481.58</v>
+        <v>362.26</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>963.16</v>
+        <v>724.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1752,64 +1752,64 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>1410.15</v>
+        <v>374.23</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>4230.45</v>
+        <v>748.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>350.05</v>
+        <v>420.87</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>350.05</v>
+        <v>1683.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1818,86 +1818,86 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>254.71</v>
+        <v>2027.12</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>509.42</v>
+        <v>6081.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>2393.79</v>
+        <v>1746.58</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2393.79</v>
+        <v>1746.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1531.7</v>
+        <v>2804.71</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>4595.1</v>
+        <v>2804.71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -1907,28 +1907,28 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>1316.56</v>
+        <v>2312.85</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>3949.68</v>
+        <v>9251.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -1938,28 +1938,28 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>2208.37</v>
+        <v>267.34</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>6625.11</v>
+        <v>534.6799999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -1969,126 +1969,126 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>986.24</v>
+        <v>1599.66</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>1972.48</v>
+        <v>3199.32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>1721.45</v>
+        <v>2029.29</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>6885.8</v>
+        <v>8117.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1477.02</v>
+        <v>1057.09</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>4431.06</v>
+        <v>3171.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1679.7</v>
+        <v>1855.32</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>3359.4</v>
+        <v>1855.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2097,210 +2097,210 @@
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>2280.75</v>
+        <v>128.72</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>9123</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>687.14</v>
+        <v>724.99</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1374.28</v>
+        <v>1449.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>运动短裤</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>1605.84</v>
+        <v>976.14</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>6423.36</v>
+        <v>2928.42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>775.67</v>
+        <v>1257.27</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>775.67</v>
+        <v>3771.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>597.88</v>
+        <v>1500.99</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>2391.52</v>
+        <v>4502.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>908.85</v>
+        <v>472.18</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>2726.55</v>
+        <v>1888.72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>843.7</v>
+        <v>922.1900000000001</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>843.7</v>
+        <v>1844.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -2310,28 +2310,28 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2620.98</v>
+        <v>1603.08</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>7862.94</v>
+        <v>6412.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -2341,312 +2341,312 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>2896.53</v>
+        <v>2768.01</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>8689.59</v>
+        <v>8304.030000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>249.02</v>
+        <v>1149.19</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>249.02</v>
+        <v>1149.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>380.8</v>
+        <v>2611.34</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>1523.2</v>
+        <v>7834.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>912.14</v>
+        <v>2247.23</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>3648.56</v>
+        <v>8988.92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>2843.34</v>
+        <v>1668.68</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>5686.68</v>
+        <v>5006.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>545.23</v>
+        <v>1097.14</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>545.23</v>
+        <v>4388.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>1424.64</v>
+        <v>1129.99</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>1424.64</v>
+        <v>4519.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>2070.53</v>
+        <v>803.5</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>6211.59</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>1952.48</v>
+        <v>1157.12</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>5857.44</v>
+        <v>2314.24</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>1796.28</v>
+        <v>2899.53</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>5388.84</v>
+        <v>11598.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -2658,26 +2658,26 @@
         <v>4</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>2828.75</v>
+        <v>2168.33</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>11315</v>
+        <v>8673.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -2689,57 +2689,57 @@
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>1822.03</v>
+        <v>2521.03</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>1822.03</v>
+        <v>2521.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>148.49</v>
+        <v>2531.36</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>296.98</v>
+        <v>5062.72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2748,60 +2748,60 @@
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>2989.93</v>
+        <v>1531.03</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>11959.72</v>
+        <v>4593.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>1018.93</v>
+        <v>48.64</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>1018.93</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -2813,233 +2813,233 @@
         <v>4</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>1996.87</v>
+        <v>79.91</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>7987.48</v>
+        <v>319.64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>989.12</v>
+        <v>744.6799999999999</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>3956.48</v>
+        <v>2234.04</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>586.12</v>
+        <v>2878.11</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>1758.36</v>
+        <v>11512.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>822.16</v>
+        <v>1970.6</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>1644.32</v>
+        <v>1970.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2919.25</v>
+        <v>1442.74</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>5838.5</v>
+        <v>1442.74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>305.83</v>
+        <v>1709.59</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>305.83</v>
+        <v>1709.59</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>1540.35</v>
+        <v>834.15</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>4621.05</v>
+        <v>834.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>1385.66</v>
+        <v>75.5</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>2771.32</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
@@ -3054,214 +3054,214 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>2323.85</v>
+        <v>511.48</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>9295.4</v>
+        <v>1022.96</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>2185.37</v>
+        <v>2376.78</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>8741.48</v>
+        <v>2376.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>蜂蜜柚子茶</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>1668.19</v>
+        <v>2519.86</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>6672.76</v>
+        <v>7559.58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E81" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>1166.42</v>
+        <v>2356.14</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>4665.68</v>
+        <v>9424.559999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>2964.59</v>
+        <v>1311.59</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>5929.18</v>
+        <v>5246.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>望远镜</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>1015.02</v>
+        <v>272.65</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>1015.02</v>
+        <v>545.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>iPad Air</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>1246.64</v>
+        <v>1100.28</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>2493.28</v>
+        <v>1100.28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>燕窝</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -3271,307 +3271,307 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>2086.33</v>
+        <v>332.63</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>2086.33</v>
+        <v>332.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>2619.98</v>
+        <v>1550.95</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>2619.98</v>
+        <v>1550.95</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>1317.9</v>
+        <v>1801.87</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1317.9</v>
+        <v>5405.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>165.59</v>
+        <v>2343.13</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>165.59</v>
+        <v>4686.26</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>754.27</v>
+        <v>827.6900000000001</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>3017.08</v>
+        <v>2483.07</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>2615.39</v>
+        <v>848.61</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>5230.78</v>
+        <v>2545.83</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E91" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>1923.58</v>
+        <v>2833.34</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>7694.32</v>
+        <v>11333.36</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>2041.5</v>
+        <v>49.1</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>4083</v>
+        <v>196.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>1926.65</v>
+        <v>1023.17</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>7706.6</v>
+        <v>2046.34</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>2563.41</v>
+        <v>556.58</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>2563.41</v>
+        <v>2226.32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3581,59 +3581,59 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>2977.3</v>
+        <v>996.88</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>8931.9</v>
+        <v>2990.64</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>有机牛奶</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>1709.81</v>
+        <v>1787.91</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>1709.81</v>
+        <v>3575.82</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -3643,28 +3643,28 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>2410.74</v>
+        <v>2398.13</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>4821.48</v>
+        <v>2398.13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
@@ -3674,28 +3674,28 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>2712.11</v>
+        <v>747.8</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>2712.11</v>
+        <v>1495.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
@@ -3705,59 +3705,59 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>1112.64</v>
+        <v>2971.38</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>2225.28</v>
+        <v>11885.52</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>625.36</v>
+        <v>2377.44</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>1876.08</v>
+        <v>7132.32</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -3767,23 +3767,23 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>2902.13</v>
+        <v>1950.59</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>8706.389999999999</v>
+        <v>1950.59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
@@ -3798,214 +3798,214 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>447.05</v>
+        <v>60.33</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>894.1</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>70.34</v>
+        <v>1190.67</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>70.34</v>
+        <v>2381.34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2471.58</v>
+        <v>1264.45</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>7414.74</v>
+        <v>1264.45</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>1869.05</v>
+        <v>1047.91</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>5607.15</v>
+        <v>2095.82</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>1957.24</v>
+        <v>2173.32</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>1957.24</v>
+        <v>8693.280000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>AirPods Pro</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>373.88</v>
+        <v>96.08</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>747.76</v>
+        <v>288.24</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>1273.81</v>
+        <v>547.13</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>2547.62</v>
+        <v>1094.26</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
@@ -4015,79 +4015,79 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>1241.1</v>
+        <v>2398.33</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>3723.3</v>
+        <v>4796.66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>1349.75</v>
+        <v>2219.04</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>2699.5</v>
+        <v>4438.08</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>羽毛球拍</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>208.83</v>
+        <v>2122.06</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>626.49</v>
+        <v>4244.12</v>
       </c>
     </row>
   </sheetData>

--- a/practice-files/day06-透视表基础.xlsx
+++ b/practice-files/day06-透视表基础.xlsx
@@ -683,17 +683,17 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>AirPods Pro</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -705,274 +705,274 @@
         <v>2</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>2817.68</v>
+        <v>1966.33</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>5635.36</v>
+        <v>3932.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>瑜伽垫</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>163.55</v>
+        <v>2990.6</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>327.1</v>
+        <v>11962.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>iPhone 15</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>471.35</v>
+        <v>915.22</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>942.7</v>
+        <v>915.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2971.13</v>
+        <v>1495.92</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>8913.389999999999</v>
+        <v>2991.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1439.43</v>
+        <v>511.61</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1439.43</v>
+        <v>2046.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毛巾</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>942.8</v>
+        <v>2377.58</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>942.8</v>
+        <v>4755.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1455.93</v>
+        <v>1002.94</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>5823.72</v>
+        <v>4011.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2845.17</v>
+        <v>2808.4</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2845.17</v>
+        <v>2808.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>红酒</t>
+          <t>收纳箱</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>478.75</v>
+        <v>2862.48</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>957.5</v>
+        <v>8587.440000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>iPad Air</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -981,179 +981,179 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1569.49</v>
+        <v>2012.32</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>4708.47</v>
+        <v>8049.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1394.2</v>
+        <v>2079.16</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>4182.6</v>
+        <v>6237.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>600.02</v>
+        <v>1449.2</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1200.04</v>
+        <v>5796.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>2319.39</v>
+        <v>2291.72</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>4638.78</v>
+        <v>2291.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>橄榄油</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2802.09</v>
+        <v>362.26</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>8406.27</v>
+        <v>724.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>2864.19</v>
+        <v>374.23</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5728.38</v>
+        <v>748.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -1163,28 +1163,28 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2773.31</v>
+        <v>420.87</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>8319.93</v>
+        <v>1683.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1194,33 +1194,33 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2800.08</v>
+        <v>2027.12</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>8400.24</v>
+        <v>6081.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1229,55 +1229,55 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>2018.41</v>
+        <v>1746.58</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4036.82</v>
+        <v>1746.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2159.55</v>
+        <v>2804.71</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2159.55</v>
+        <v>2804.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1287,152 +1287,152 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>1447.02</v>
+        <v>2312.85</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>2894.04</v>
+        <v>9251.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>AirPods Pro</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1966.33</v>
+        <v>267.34</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>3932.66</v>
+        <v>534.6799999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>2990.6</v>
+        <v>1599.66</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>11962.4</v>
+        <v>3199.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>iPhone 15</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>915.22</v>
+        <v>2029.29</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>915.22</v>
+        <v>8117.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1495.92</v>
+        <v>1057.09</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>2991.84</v>
+        <v>3171.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>机械键盘</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1442,28 +1442,28 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>511.61</v>
+        <v>1855.32</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>2046.44</v>
+        <v>1855.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -1473,28 +1473,28 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>2377.58</v>
+        <v>128.72</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>4755.16</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1504,152 +1504,152 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1002.94</v>
+        <v>724.99</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>4011.76</v>
+        <v>1449.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>运动短裤</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>2808.4</v>
+        <v>976.14</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>2808.4</v>
+        <v>2928.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>收纳箱</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2862.48</v>
+        <v>1257.27</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>8587.440000000001</v>
+        <v>3771.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>2012.32</v>
+        <v>1500.99</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>8049.28</v>
+        <v>4502.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2079.16</v>
+        <v>472.18</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>6237.48</v>
+        <v>1888.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>T恤纯棉</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -1659,333 +1659,333 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>1449.2</v>
+        <v>922.1900000000001</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>5796.8</v>
+        <v>1844.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>2291.72</v>
+        <v>1603.08</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>2291.72</v>
+        <v>6412.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>362.26</v>
+        <v>2768.01</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>724.52</v>
+        <v>8304.030000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>374.23</v>
+        <v>1149.19</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>748.46</v>
+        <v>1149.19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>420.87</v>
+        <v>2611.34</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>1683.48</v>
+        <v>7834.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>2027.12</v>
+        <v>2247.23</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>6081.36</v>
+        <v>8988.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>1746.58</v>
+        <v>1668.68</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>1746.58</v>
+        <v>5006.04</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>瑜伽垫</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>2804.71</v>
+        <v>1097.14</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>2804.71</v>
+        <v>4388.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E41" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>2312.85</v>
+        <v>1129.99</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>9251.4</v>
+        <v>4519.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>运动跑鞋</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>267.34</v>
+        <v>803.5</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>534.6799999999999</v>
+        <v>3214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E43" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>1599.66</v>
+        <v>1157.12</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>3199.32</v>
+        <v>2314.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2000,28 +2000,28 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>2029.29</v>
+        <v>2899.53</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>8117.16</v>
+        <v>11598.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -2031,152 +2031,152 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E45" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1057.09</v>
+        <v>2168.33</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>3171.27</v>
+        <v>8673.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>机械键盘</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1855.32</v>
+        <v>2521.03</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1855.32</v>
+        <v>2521.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>移动硬盘</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>128.72</v>
+        <v>2531.36</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>128.72</v>
+        <v>5062.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>加湿器</t>
+          <t>MacBook Pro</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>724.99</v>
+        <v>1531.03</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1449.98</v>
+        <v>4593.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>运动短裤</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E49" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>976.14</v>
+        <v>48.64</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>2928.42</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>游泳镜</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2186,95 +2186,95 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1257.27</v>
+        <v>79.91</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>3771.81</v>
+        <v>319.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E51" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1500.99</v>
+        <v>744.6799999999999</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>4502.97</v>
+        <v>2234.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>小米14</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>472.18</v>
+        <v>2878.11</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>1888.72</v>
+        <v>11512.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T恤纯棉</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2283,19 +2283,19 @@
         </is>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>922.1900000000001</v>
+        <v>1970.6</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>1844.38</v>
+        <v>1970.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -2310,33 +2310,33 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>1603.08</v>
+        <v>1442.74</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>6412.32</v>
+        <v>1442.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2345,117 +2345,117 @@
         </is>
       </c>
       <c r="E55" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>2768.01</v>
+        <v>1709.59</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>8304.030000000001</v>
+        <v>1709.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>1149.19</v>
+        <v>834.15</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>1149.19</v>
+        <v>834.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>卫衣连帽</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>2611.34</v>
+        <v>75.5</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>7834.02</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>2247.23</v>
+        <v>511.48</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>8988.92</v>
+        <v>1022.96</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>空气净化器</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -2465,214 +2465,214 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E59" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>1668.68</v>
+        <v>2376.78</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>5006.04</v>
+        <v>2376.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>1097.14</v>
+        <v>2519.86</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>4388.56</v>
+        <v>7559.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E61" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>1129.99</v>
+        <v>2356.14</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>4519.96</v>
+        <v>9424.559999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>运动跑鞋</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>803.5</v>
+        <v>1311.59</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>3214</v>
+        <v>5246.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>咖啡豆</t>
+          <t>羽绒服</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E63" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>1157.12</v>
+        <v>272.65</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>2314.24</v>
+        <v>545.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2899.53</v>
+        <v>1100.28</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>11598.12</v>
+        <v>1100.28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E65" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>2168.33</v>
+        <v>332.63</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>8673.32</v>
+        <v>332.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>瑜伽垫</t>
+          <t>防晒衣</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -2682,126 +2682,126 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2521.03</v>
+        <v>1550.95</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>2521.03</v>
+        <v>1550.95</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E67" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>2531.36</v>
+        <v>1801.87</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>5062.72</v>
+        <v>5405.61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>MacBook Pro</t>
+          <t>扫地机器人</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>1531.03</v>
+        <v>2343.13</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>4593.09</v>
+        <v>4686.26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E69" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>48.64</v>
+        <v>827.6900000000001</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>194.56</v>
+        <v>2483.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>游泳镜</t>
+          <t>休闲皮鞋</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -2810,86 +2810,86 @@
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>79.91</v>
+        <v>848.61</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>319.64</v>
+        <v>2545.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>帐篷</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E71" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>744.6799999999999</v>
+        <v>2833.34</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>2234.04</v>
+        <v>11333.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>小米14</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>2878.11</v>
+        <v>49.1</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>11512.44</v>
+        <v>196.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>坚果礼盒</t>
+          <t>蛋白粉</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -2899,28 +2899,28 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>1970.6</v>
+        <v>1023.17</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>1970.6</v>
+        <v>2046.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>地毯</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -2934,55 +2934,55 @@
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>1442.74</v>
+        <v>556.58</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>1442.74</v>
+        <v>2226.32</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>1709.59</v>
+        <v>996.88</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>1709.59</v>
+        <v>2990.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>滑雪手套</t>
+          <t>跑步腰包</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -2992,28 +2992,28 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>834.15</v>
+        <v>1787.91</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>834.15</v>
+        <v>3575.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>卫衣连帽</t>
+          <t>棒球帽</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -3023,126 +3023,126 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>75.5</v>
+        <v>2398.13</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>151</v>
+        <v>2398.13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>511.48</v>
+        <v>747.8</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>1022.96</v>
+        <v>1495.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>空气净化器</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>2376.78</v>
+        <v>2971.38</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>2376.78</v>
+        <v>11885.52</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E80" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>2519.86</v>
+        <v>2377.44</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>7559.58</v>
+        <v>7132.32</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>绿茶龙井</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -3151,112 +3151,112 @@
         </is>
       </c>
       <c r="E81" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>2356.14</v>
+        <v>1950.59</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>9424.559999999999</v>
+        <v>1950.59</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>头盔</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E82" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>1311.59</v>
+        <v>60.33</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>5246.36</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>羽绒服</t>
+          <t>四件套</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E83" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>272.65</v>
+        <v>1190.67</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>545.3</v>
+        <v>2381.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>1100.28</v>
+        <v>1264.45</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1100.28</v>
+        <v>1264.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -3275,91 +3275,91 @@
         </is>
       </c>
       <c r="E85" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>332.63</v>
+        <v>1047.91</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>332.63</v>
+        <v>2095.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>防晒衣</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E86" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>1550.95</v>
+        <v>2173.32</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>1550.95</v>
+        <v>8693.280000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>登山包</t>
+          <t>AirPods Pro</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E87" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>1801.87</v>
+        <v>96.08</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>5405.61</v>
+        <v>288.24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>扫地机器人</t>
+          <t>围巾</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -3371,88 +3371,88 @@
         <v>2</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>2343.13</v>
+        <v>547.13</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>4686.26</v>
+        <v>1094.26</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>牛仔裤</t>
+          <t>台灯LED</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>827.6900000000001</v>
+        <v>2398.33</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>2483.07</v>
+        <v>4796.66</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>休闲皮鞋</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>848.61</v>
+        <v>2219.04</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>2545.83</v>
+        <v>4438.08</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>乳胶枕头</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -3461,91 +3461,91 @@
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>2833.34</v>
+        <v>2122.06</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>11333.36</v>
+        <v>4244.12</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>登山包</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>49.1</v>
+        <v>2403.52</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>196.4</v>
+        <v>4807.04</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>蛋白粉</t>
+          <t>蚕丝被</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>1023.17</v>
+        <v>808.1900000000001</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>2046.34</v>
+        <v>3232.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -3554,24 +3554,24 @@
         </is>
       </c>
       <c r="E94" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>556.58</v>
+        <v>1772.4</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>2226.32</v>
+        <v>5317.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>帐篷</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -3581,333 +3581,333 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>996.88</v>
+        <v>2445.8</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>2990.64</v>
+        <v>7337.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>跑步腰包</t>
+          <t>坚果礼盒</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>1787.91</v>
+        <v>737.5599999999999</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>3575.82</v>
+        <v>737.5599999999999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>棒球帽</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>2398.13</v>
+        <v>1271.17</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>2398.13</v>
+        <v>2542.34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>冲锋衣</t>
+          <t>地毯</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>747.8</v>
+        <v>2088.5</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>1495.6</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>蓝牙音箱</t>
+          <t>牛仔裤</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>2971.38</v>
+        <v>963.3</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>11885.52</v>
+        <v>3853.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>瑜伽垫</t>
+          <t>蓝牙音箱</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>运动户外</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>2377.44</v>
+        <v>434.51</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>7132.32</v>
+        <v>1738.04</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>绿茶龙井</t>
+          <t>加湿器</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>家居用品</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>1950.59</v>
+        <v>1480.44</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>1950.59</v>
+        <v>1480.44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>蚕丝被</t>
+          <t>有机牛奶</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>60.33</v>
+        <v>845.3099999999999</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>180.99</v>
+        <v>2535.93</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>四件套</t>
+          <t>滑雪手套</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>1190.67</v>
+        <v>1661.69</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>2381.34</v>
+        <v>1661.69</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>华为Mate 60</t>
+          <t>瑜伽垫</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>1264.45</v>
+        <v>2286.21</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>1264.45</v>
+        <v>9144.84</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>巧克力</t>
+          <t>冲锋衣</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>食品饮料</t>
+          <t>服装鞋帽</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>1047.91</v>
+        <v>2627.19</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>2095.82</v>
+        <v>2627.19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
@@ -3922,95 +3922,95 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>2173.32</v>
+        <v>2598.91</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>8693.280000000001</v>
+        <v>2598.91</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>AirPods Pro</t>
+          <t>头盔</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>电子产品</t>
+          <t>运动户外</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>96.08</v>
+        <v>521.97</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>288.24</v>
+        <v>1043.94</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>围巾</t>
+          <t>移动硬盘</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>服装鞋帽</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>547.13</v>
+        <v>1070.92</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>1094.26</v>
+        <v>3212.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>台灯LED</t>
+          <t>燕窝</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4019,75 +4019,75 @@
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>2398.33</v>
+        <v>823.01</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>4796.66</v>
+        <v>823.01</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>华为Mate 60</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>电子产品</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>2219.04</v>
+        <v>2604.13</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>4438.08</v>
+        <v>5208.26</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>乳胶枕头</t>
+          <t>咖啡豆</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>家居用品</t>
+          <t>食品饮料</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>2122.06</v>
+        <v>2290.58</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>4244.12</v>
+        <v>9162.32</v>
       </c>
     </row>
   </sheetData>
